--- a/engineer_forms/009_switchgear_inspection_form--engineer_forms.xlsx
+++ b/engineer_forms/009_switchgear_inspection_form--engineer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>switchgear_inspection_form_page</t>
+          <t>switchgear_item_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>switchgear_inspection_form_page</t>
+          <t>What is the name of the switchgear item?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>switchgear_item</t>
+          <t>switchgear_location_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>switchgear_item</t>
+          <t>Where was the switchgear item inspected?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>switchgear_location</t>
+          <t>switchgear_condition_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>switchgear_location</t>
+          <t>What was the condition of the switchgear item during inspection?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>switchgear_condition</t>
+          <t>switchgear_inspection_type_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>switchgear_condition</t>
+          <t>What type of inspection was performed on the switchgear item?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,127 +612,127 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type</t>
+          <t>switchgear_result_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type</t>
+          <t>What was the result of the inspection?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>switchgear_inspection_date</t>
+          <t>switchgear_status_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>switchgear_inspection_date</t>
+          <t>What is the status of the inspection?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>switchgear_inspection_time</t>
+          <t>switchgear_recommendation_action_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>switchgear_inspection_time</t>
+          <t>What is the recommended action for the switchgear item?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>switchgear_inspection_note</t>
+          <t>switchgear_recommendation_date_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>switchgear_inspection_note</t>
+          <t>What is the date of the inspection recommendation?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>switchgear_inspection_result</t>
+          <t>switchgear_recommendation_time_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>switchgear_inspection_result</t>
+          <t>What is the time of the inspection recommendation?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>switchgear_inspection_status</t>
+          <t>switchgear_recommendation_note_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>switchgear_inspection_status</t>
+          <t>Is there a note for the inspection recommendation?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>switchgear_inspection_comment</t>
+          <t>switchgear_recommendation_comments_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>switchgear_inspection_comment</t>
+          <t>Are there any comments for the inspection recommendation?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation</t>
+          <t>switchgear_recommendation_status_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation</t>
+          <t>What is the status of the inspection recommendation?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_action</t>
+          <t>switchgear_recommendation_comments_page_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_action</t>
+          <t>Switchgear Recommendation Comments Page 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_status</t>
+          <t>switchgear_recommendation_comments_text_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_status</t>
+          <t>Switchgear Recommendation Comments Text Page</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,23 +837,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_comments</t>
+          <t>switchgear_result_page_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_comments</t>
+          <t>What is the result of the inspection?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_date</t>
+          <t>switchgear_recommendation_date_page_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_date</t>
+          <t>Switchgear Recommendation Date Page 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_time</t>
+          <t>switchgear_recommendation_time_page_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_time</t>
+          <t>Switchgear Recommendation Time Page 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_note</t>
+          <t>switchgear_recommendation_note_page_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_note</t>
+          <t>Switchgear Recommendation Note Page 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_result</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_result</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_status</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_comments_text_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_result_text</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_result_text</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,357 +965,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_inspection_type_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>visual_inspection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>Visual Inspection</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_inspection_type_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>mechanical_inspection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>Mechanical Inspection</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_inspection_type_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>functional_inspection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>Functional Inspection</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_result_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item4</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>item4</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_result_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item5</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>item5</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>switchgear_inspection_type_choices</t>
+          <t>switchgear_result_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item6</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>item6</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>switchgear_inspection_result_choices</t>
+          <t>switchgear_status_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>switchgear_inspection_result_choices</t>
+          <t>switchgear_status_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>switchgear_inspection_result_choices</t>
+          <t>switchgear_status_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>switchgear_inspection_status_choices</t>
+          <t>switchgear_recommendation_status_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>switchgear_inspection_status_choices</t>
+          <t>switchgear_recommendation_status_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>switchgear_inspection_status_choices</t>
+          <t>switchgear_recommendation_status_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
+          <t>switchgear_result_page_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
+          <t>switchgear_result_page_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
+          <t>switchgear_result_page_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_result_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_result_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_result_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>switchgear_inspection_recommendation_status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>item3</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
